--- a/artfynd/A 15591-2023 artfynd.xlsx
+++ b/artfynd/A 15591-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129023391</v>
       </c>
       <c r="B2" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129023393</v>
       </c>
       <c r="B3" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129023371</v>
       </c>
       <c r="B4" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Petter Lindwall, David Kenger, Edvin Strandberg</t>
+          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1111,7 +1111,7 @@
         <v>129088696</v>
       </c>
       <c r="B6" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Petter Lindwall, David Kenger, Edvin Strandberg</t>
+          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 15591-2023 artfynd.xlsx
+++ b/artfynd/A 15591-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129023391</v>
       </c>
       <c r="B2" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129023393</v>
       </c>
       <c r="B3" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129023371</v>
       </c>
       <c r="B4" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129088697</v>
       </c>
       <c r="B5" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
+          <t>Petter Lindwall, David Kenger, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1111,7 +1111,7 @@
         <v>129088696</v>
       </c>
       <c r="B6" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Edvin Strandberg, David Kenger, Petter Lindwall</t>
+          <t>Petter Lindwall, David Kenger, Edvin Strandberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 15591-2023 artfynd.xlsx
+++ b/artfynd/A 15591-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129023391</v>
       </c>
       <c r="B2" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129023393</v>
       </c>
       <c r="B3" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129023371</v>
       </c>
       <c r="B4" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129088697</v>
       </c>
       <c r="B5" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>129088696</v>
       </c>
       <c r="B6" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 15591-2023 artfynd.xlsx
+++ b/artfynd/A 15591-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129023391</v>
       </c>
       <c r="B2" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129023393</v>
       </c>
       <c r="B3" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129023371</v>
       </c>
       <c r="B4" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>129088696</v>
       </c>
       <c r="B6" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 15591-2023 artfynd.xlsx
+++ b/artfynd/A 15591-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129023391</v>
       </c>
       <c r="B2" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129023393</v>
       </c>
       <c r="B3" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129023371</v>
       </c>
       <c r="B4" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129088697</v>
       </c>
       <c r="B5" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>129088696</v>
       </c>
       <c r="B6" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 15591-2023 artfynd.xlsx
+++ b/artfynd/A 15591-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129023391</v>
       </c>
       <c r="B2" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129023393</v>
       </c>
       <c r="B3" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129023371</v>
       </c>
       <c r="B4" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>129088696</v>
       </c>
       <c r="B6" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 15591-2023 artfynd.xlsx
+++ b/artfynd/A 15591-2023 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>129023393</v>
       </c>
       <c r="B3" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,14 +802,10 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>

--- a/artfynd/A 15591-2023 artfynd.xlsx
+++ b/artfynd/A 15591-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129023391</v>
       </c>
       <c r="B2" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129023393</v>
       </c>
       <c r="B3" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>129023371</v>
       </c>
       <c r="B4" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>129088697</v>
       </c>
       <c r="B5" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>129088696</v>
       </c>
       <c r="B6" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 15591-2023 artfynd.xlsx
+++ b/artfynd/A 15591-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1775,6 +1775,335 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>131366428</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57881</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bergsboda, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>763036</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7082264</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Umeå stad</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Födsöksspår på stående död gran.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>131366468</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58043</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bergsboda, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>763039</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7082237</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Umeå stad</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>131366420</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57881</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Bergsboda, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>763052</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7082241</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Umeå stad</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Spår på avbarkad gran</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 15591-2023 artfynd.xlsx
+++ b/artfynd/A 15591-2023 artfynd.xlsx
@@ -1219,7 +1219,7 @@
         <v>131321686</v>
       </c>
       <c r="B7" t="n">
-        <v>91777</v>
+        <v>91779</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>131321684</v>
       </c>
       <c r="B8" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         <v>131321677</v>
       </c>
       <c r="B9" t="n">
-        <v>91777</v>
+        <v>91779</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>131321669</v>
       </c>
       <c r="B10" t="n">
-        <v>91777</v>
+        <v>91779</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>131321688</v>
       </c>
       <c r="B11" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
         <v>131366428</v>
       </c>
       <c r="B12" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>131366468</v>
       </c>
       <c r="B13" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>131366420</v>
       </c>
       <c r="B14" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 15591-2023 artfynd.xlsx
+++ b/artfynd/A 15591-2023 artfynd.xlsx
@@ -1219,7 +1219,7 @@
         <v>131321686</v>
       </c>
       <c r="B7" t="n">
-        <v>91779</v>
+        <v>91780</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>131321684</v>
       </c>
       <c r="B8" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         <v>131321677</v>
       </c>
       <c r="B9" t="n">
-        <v>91779</v>
+        <v>91780</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>131321669</v>
       </c>
       <c r="B10" t="n">
-        <v>91779</v>
+        <v>91780</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>131321688</v>
       </c>
       <c r="B11" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
         <v>131366428</v>
       </c>
       <c r="B12" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>131366468</v>
       </c>
       <c r="B13" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>131366420</v>
       </c>
       <c r="B14" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 15591-2023 artfynd.xlsx
+++ b/artfynd/A 15591-2023 artfynd.xlsx
@@ -1219,7 +1219,7 @@
         <v>131321686</v>
       </c>
       <c r="B7" t="n">
-        <v>91780</v>
+        <v>91781</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>131321684</v>
       </c>
       <c r="B8" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         <v>131321677</v>
       </c>
       <c r="B9" t="n">
-        <v>91780</v>
+        <v>91781</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>131321669</v>
       </c>
       <c r="B10" t="n">
-        <v>91780</v>
+        <v>91781</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>131321688</v>
       </c>
       <c r="B11" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
         <v>131366428</v>
       </c>
       <c r="B12" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>131366468</v>
       </c>
       <c r="B13" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>131366420</v>
       </c>
       <c r="B14" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 15591-2023 artfynd.xlsx
+++ b/artfynd/A 15591-2023 artfynd.xlsx
@@ -1219,7 +1219,7 @@
         <v>131321686</v>
       </c>
       <c r="B7" t="n">
-        <v>91781</v>
+        <v>91784</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>131321684</v>
       </c>
       <c r="B8" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         <v>131321677</v>
       </c>
       <c r="B9" t="n">
-        <v>91781</v>
+        <v>91784</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>131321669</v>
       </c>
       <c r="B10" t="n">
-        <v>91781</v>
+        <v>91784</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>131321688</v>
       </c>
       <c r="B11" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
         <v>131366428</v>
       </c>
       <c r="B12" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>131366468</v>
       </c>
       <c r="B13" t="n">
-        <v>58047</v>
+        <v>58050</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>131366420</v>
       </c>
       <c r="B14" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 15591-2023 artfynd.xlsx
+++ b/artfynd/A 15591-2023 artfynd.xlsx
@@ -1219,7 +1219,7 @@
         <v>131321686</v>
       </c>
       <c r="B7" t="n">
-        <v>91784</v>
+        <v>91785</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>131321684</v>
       </c>
       <c r="B8" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         <v>131321677</v>
       </c>
       <c r="B9" t="n">
-        <v>91784</v>
+        <v>91785</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>131321669</v>
       </c>
       <c r="B10" t="n">
-        <v>91784</v>
+        <v>91785</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>131321688</v>
       </c>
       <c r="B11" t="n">
-        <v>91841</v>
+        <v>91842</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
         <v>131366428</v>
       </c>
       <c r="B12" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>131366468</v>
       </c>
       <c r="B13" t="n">
-        <v>58050</v>
+        <v>58051</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>131366420</v>
       </c>
       <c r="B14" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
